--- a/TIME TABLE SAMPLE DATA/INPUTS/subject-continuous-rules-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/INPUTS/subject-continuous-rules-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajas\OneDrive\Desktop\Timetable\TIME TABLE SAMPLE DATA\INPUTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7651C9-299A-4F13-872D-C9A0765F0955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CD2711-5D47-47BC-A16B-9AEC98283C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -388,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" customWidth="1"/>
@@ -403,14 +403,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TIME TABLE SAMPLE DATA/INPUTS/subject-continuous-rules-template.xlsx
+++ b/TIME TABLE SAMPLE DATA/INPUTS/subject-continuous-rules-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajas\OneDrive\Desktop\Timetable\TIME TABLE SAMPLE DATA\INPUTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/INPUTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CD2711-5D47-47BC-A16B-9AEC98283C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{19CD2711-5D47-47BC-A16B-9AEC98283C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5EF91CA-AF3F-4C70-A46A-6BC0DC3BCC52}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -388,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" customWidth="1"/>
@@ -403,6 +403,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
